--- a/03_Charts/VAE/FinancialRatios/XGBoost/StrategyB/Error_Summary.xlsx
+++ b/03_Charts/VAE/FinancialRatios/XGBoost/StrategyB/Error_Summary.xlsx
@@ -20,19 +20,19 @@
     <t xml:space="preserve">Count</t>
   </si>
   <si>
+    <t xml:space="preserve">Median_Net Debt Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median_Return on Assets (ROA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median_Return on Fixed Assets</t>
+  </si>
+  <si>
     <t xml:space="preserve">Median_Self-Financing Ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">Median_Return on Fixed Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_Inventory Intensity</t>
-  </si>
-  <si>
     <t xml:space="preserve">Median_Cash to Current Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median_Return on Assets (ROA)</t>
   </si>
   <si>
     <t xml:space="preserve">True Negative</t>
@@ -401,22 +401,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>137885</v>
+        <v>129267</v>
       </c>
       <c r="C2" t="n">
-        <v>0.190995825879547</v>
+        <v>-0.235475354068855</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0889084507042254</v>
+        <v>0.181506397258587</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0192023633677991</v>
+        <v>0.142966897880561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.187633262260128</v>
+        <v>0.225754608636854</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0401384083044983</v>
+        <v>0.190434013226489</v>
       </c>
     </row>
     <row r="3">
@@ -424,22 +424,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>22145</v>
+        <v>30763</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.20976253298153</v>
+        <v>0.970952950854674</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.150943396226415</v>
+        <v>-0.986030061567282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0589988081048868</v>
+        <v>-1.01314728716747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0136986301369863</v>
+        <v>-1.0548945186846</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0585585585585586</v>
+        <v>-0.664298596183873</v>
       </c>
     </row>
     <row r="4">
@@ -447,22 +447,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C4" t="n">
-        <v>0.142358794386975</v>
+        <v>0.122113538253114</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0385952562242303</v>
+        <v>-0.071834318373541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00538374629727062</v>
+        <v>-0.0456667425702114</v>
       </c>
       <c r="F4" t="n">
-        <v>0.146027831601198</v>
+        <v>0.00309826981267122</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0223643770459416</v>
+        <v>0.0265053035229723</v>
       </c>
     </row>
     <row r="5">
@@ -470,22 +470,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1234</v>
+        <v>1221</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.171112951900626</v>
+        <v>1.00188610913077</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.125207273544869</v>
+        <v>-1.14536751217818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0457134377296625</v>
+        <v>-1.13406893873461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0179984286265645</v>
+        <v>-1.13903131216401</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0520469188910774</v>
+        <v>-0.620364681457114</v>
       </c>
     </row>
   </sheetData>
